--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3388.55</v>
+        <v>3437.04</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5137.35</v>
+        <v>5197.61</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>35961.44</v>
+        <v>36383.29</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4207.36</v>
+        <v>4256.71</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12875.56</v>
+        <v>13093.32</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>19718.62</v>
+        <v>20052.11</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2976.3</v>
+        <v>3006.57</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8327.379999999999</v>
+        <v>8412.059999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6857.06</v>
+        <v>6926.79</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>63228.9</v>
+        <v>63871.9</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2939.43</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4894.97</v>
+        <v>4940.88</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6437.49</v>
+        <v>6388.66</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4149.17</v>
+        <v>4079.07</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2648.4</v>
+        <v>2603.65</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2634.54</v>
+        <v>2590.03</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4947.48</v>
+        <v>4863.89</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4514.77</v>
+        <v>4450.7</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5137.35</v>
+        <v>5064.44</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2660.88</v>
+        <v>2624.32</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>30463.28</v>
+        <v>30044.7</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2765.89</v>
+        <v>2727.89</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4291.66</v>
+        <v>4232.69</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5637.91</v>
+        <v>5602.96</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>7993.58</v>
+        <v>7944.02</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3721.91</v>
+        <v>3698.83</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3613.2</v>
+        <v>3590.8</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3367.6</v>
+        <v>3382.89</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2634.54</v>
+        <v>2673.77</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3215.03</v>
+        <v>3262.91</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2529.16</v>
+        <v>2566.82</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7943.6</v>
+        <v>8061.89</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2411.39</v>
+        <v>2457.24</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3103.62</v>
+        <v>3162.62</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2473.74</v>
+        <v>2529.53</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4894.97</v>
+        <v>4928.77</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5504.87</v>
+        <v>5542.87</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3913.16</v>
+        <v>3940.18</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5548.6</v>
+        <v>5586.91</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>30364.1</v>
+        <v>30573.74</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4931.85</v>
+        <v>4965.9</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2568.67</v>
+        <v>2586.41</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>29776.2</v>
+        <v>29981.78</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5788.08</v>
+        <v>5828.04</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>13551.31</v>
+        <v>13593.2</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4027.91</v>
+        <v>4040.37</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2520.92</v>
+        <v>2528.71</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4081.66</v>
+        <v>4094.28</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3951.81</v>
+        <v>3964.02</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>4339.83</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4426.15</v>
+        <v>4439.84</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8367.860000000001</v>
+        <v>8393.73</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7088.36</v>
+        <v>7110.27</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3962.63</v>
+        <v>3974.88</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4339.83</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>68958.37</v>
+        <v>68775.98</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>15065.08</v>
+        <v>15025.23</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>56234.6</v>
+        <v>56085.87</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>14643.02</v>
+        <v>14604.29</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>28242.24</v>
+        <v>28167.55</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3235.21</v>
+        <v>3192.12</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>6291.28</v>
+        <v>6207.48</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4185.38</v>
+        <v>4129.63</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5216.38</v>
+        <v>5146.9</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2419.56</v>
+        <v>2387.33</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2530.34</v>
+        <v>2496.64</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>16741.53</v>
+        <v>16518.53</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4550.58</v>
+        <v>4489.96</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>62278.48</v>
+        <v>61448.92</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>15191.8</v>
+        <v>14894.44</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2444.98</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>4324.79</v>
+        <v>4240.14</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2444.98</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5554.84</v>
+        <v>5446.11</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3806.96</v>
+        <v>3732.44</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2395.6</v>
+        <v>2348.71</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>74521.42999999999</v>
+        <v>73062.75999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>7904.67</v>
+        <v>7749.94</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>19248.06</v>
+        <v>18962.89</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>21932.53</v>
+        <v>21607.58</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>17775.25</v>
+        <v>17511.89</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>22218.85</v>
+        <v>21889.66</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>4378.38</v>
+        <v>4288.39</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>76659.10000000001</v>
+        <v>75083.63</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>46288.97</v>
+        <v>45337.65</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>55325.29</v>
+        <v>54188.26</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>47454.61</v>
+        <v>46479.34</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>30600.16</v>
+        <v>29971.27</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>5254.47</v>
+        <v>5146.48</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4550.58</v>
+        <v>4457.05</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3747,7 +3747,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057402-6514-CM26</t>
+          <t>1057402-6564-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>4353.24</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="56">
@@ -3869,7 +3869,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057402-6571-CM26</t>
+          <t>1057402-6485-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3859.73</v>
+        <v>8393.73</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057402-6485-CM26</t>
+          <t>1057402-6488-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8393.73</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057402-6488-CM26</t>
+          <t>1057402-6510-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4052,7 +4052,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057402-6510-CM26</t>
+          <t>1057402-6483-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3859.73</v>
+        <v>7110.27</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057402-6483-CM26</t>
+          <t>1057402-6571-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7110.27</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057402-6564-CM26</t>
+          <t>1057402-6565-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3859.73</v>
+        <v>3974.88</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057402-6565-CM26</t>
+          <t>1057402-6566-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3974.88</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057402-6566-CM26</t>
+          <t>1057402-6514-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4723,7 +4723,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>812030-711-CM26</t>
+          <t>1380-8108-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>6207.48</v>
+        <v>2387.33</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2111-10040-CM26</t>
+          <t>812030-711-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4129.63</v>
+        <v>6207.48</v>
       </c>
     </row>
     <row r="73">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4906,7 +4906,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1380-8108-CM26</t>
+          <t>2111-10040-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4926,32 +4926,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2387.33</v>
+        <v>4129.63</v>
       </c>
     </row>
     <row r="75">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6004,7 +6004,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2111-10164-CM26</t>
+          <t>1057489-8114-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>4288.39</v>
+        <v>5146.48</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1952-1685-CM26</t>
+          <t>5326-865-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6090,27 +6090,27 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>75083.63</v>
+        <v>29971.27</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>812030-712-CM26</t>
+          <t>5326-864-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6146,32 +6146,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>45337.65</v>
+        <v>46479.34</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057539-4947-CM26</t>
+          <t>1952-1685-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6212,17 +6212,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>54188.26</v>
+        <v>75083.63</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5326-864-CM26</t>
+          <t>812030-712-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6268,32 +6268,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>46479.34</v>
+        <v>45337.65</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5326-865-CM26</t>
+          <t>3191-3081-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6334,27 +6334,27 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>29971.27</v>
+        <v>18897.91</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057489-8114-CM26</t>
+          <t>2111-10164-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6390,17 +6390,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>5146.48</v>
+        <v>4288.39</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2111-10165-CM26</t>
+          <t>1057539-4947-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,27 +6456,27 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,6 +6486,67 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
+        <v>54188.26</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2111-10165-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
         <v>4457.05</v>
       </c>
     </row>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
@@ -806,7 +806,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2274,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2400,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2526,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2774,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2961,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3331,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3457,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4803,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5051,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +5909,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6157,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6222,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
@@ -562,7 +562,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +997,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1123,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1310,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1741,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1806,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1932,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +1997,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2062,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2249,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2465,7 +2505,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2591,7 +2635,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2900,7 +2948,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4437,7 +4489,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4498,7 +4554,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4559,7 +4619,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4620,7 +4684,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4681,7 +4749,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4868,7 +4940,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5360,7 +5436,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5482,7 +5562,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5665,7 +5749,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6287,7 +6375,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6531,7 +6623,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2965,7 +2965,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2107-1197-CM26</t>
+          <t>3191-3021-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2985,52 +2985,48 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>30573.74</v>
+        <v>5828.04</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2107-1196-CM26</t>
+          <t>2107-1197-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3070,22 +3066,26 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4965.9</v>
+        <v>30573.74</v>
       </c>
     </row>
     <row r="43">
@@ -3152,7 +3152,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2080-5727-CM26</t>
+          <t>2080-5732-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3207,13 +3207,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>29981.78</v>
+        <v>6101.27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3191-3021-CM26</t>
+          <t>2080-5727-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3233,32 +3233,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3268,13 +3268,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5828.04</v>
+        <v>29981.78</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057402-6581-CM26</t>
+          <t>2107-1196-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3299,27 +3299,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3859.73</v>
+        <v>4965.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1057539-4657-CM26</t>
+          <t>1057402-6581-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3355,52 +3355,48 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>13593.2</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057402-6695-CM26</t>
+          <t>1057539-4657-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3425,43 +3421,47 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4040.37</v>
+        <v>13593.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1057402-6694-CM26</t>
+          <t>1057402-6695-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3501,32 +3501,28 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2528.71</v>
+        <v>4040.37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3328-1493-CM26</t>
+          <t>1057402-6694-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3551,43 +3547,47 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4094.28</v>
+        <v>2528.71</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1057539-4560-CM26</t>
+          <t>3328-1493-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3612,27 +3612,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3964.02</v>
+        <v>4094.28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1057402-6588-CM26</t>
+          <t>1057539-4560-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3673,27 +3673,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3859.73</v>
+        <v>3964.02</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1057402-6584-CM26</t>
+          <t>1057402-6588-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3770,7 +3770,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057402-6577-CM26</t>
+          <t>1057402-6584-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3831,7 +3831,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057402-6564-CM26</t>
+          <t>1057402-6577-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3892,7 +3892,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057402-6569-CM26</t>
+          <t>1057402-6564-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3947,13 +3947,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4439.84</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057402-6485-CM26</t>
+          <t>1057402-6569-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4008,13 +4008,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>8393.73</v>
+        <v>4439.84</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057402-6488-CM26</t>
+          <t>1057402-6485-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4069,13 +4069,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3859.73</v>
+        <v>8393.73</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057402-6510-CM26</t>
+          <t>1057402-6488-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4136,7 +4136,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057402-6483-CM26</t>
+          <t>1057402-6510-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4191,13 +4191,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7110.27</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057402-6571-CM26</t>
+          <t>1057402-6483-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4252,13 +4252,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3859.73</v>
+        <v>7110.27</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057402-6565-CM26</t>
+          <t>1057402-6571-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4313,13 +4313,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3974.88</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057402-6566-CM26</t>
+          <t>1057402-6565-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4374,13 +4374,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4353.24</v>
+        <v>3974.88</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057402-6514-CM26</t>
+          <t>1057402-6566-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4441,7 +4441,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1549-2697-CM26</t>
+          <t>1057402-6514-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4466,47 +4466,43 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>68775.98</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1549-2703-CM26</t>
+          <t>1549-2697-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4565,13 +4561,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>15025.23</v>
+        <v>68775.98</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1549-2705-CM26</t>
+          <t>1549-2703-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4630,13 +4626,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>56085.87</v>
+        <v>15025.23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1549-2707-CM26</t>
+          <t>1549-2705-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4695,13 +4691,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>14604.29</v>
+        <v>56085.87</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1549-2709-CM26</t>
+          <t>1549-2707-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4760,13 +4756,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>28167.55</v>
+        <v>14604.29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3191-3137-CM26</t>
+          <t>1549-2709-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4781,7 +4777,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4791,43 +4787,47 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3192.12</v>
+        <v>28167.55</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1380-8108-CM26</t>
+          <t>3191-3137-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4852,47 +4852,43 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2387.33</v>
+        <v>3192.12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>812030-711-CM26</t>
+          <t>1380-8108-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4912,32 +4908,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4951,13 +4947,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>6207.48</v>
+        <v>2387.33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3191-3135-CM26</t>
+          <t>812030-711-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4982,43 +4978,47 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5146.9</v>
+        <v>6207.48</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2111-10040-CM26</t>
+          <t>3191-3135-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5038,32 +5038,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -5073,13 +5073,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4129.63</v>
+        <v>5146.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>608-7488-CM26</t>
+          <t>2111-10040-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5099,52 +5099,48 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2496.64</v>
+        <v>4129.63</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2111-9985-CM26</t>
+          <t>608-7488-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5169,43 +5165,47 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>16518.53</v>
+        <v>2496.64</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3328-1542-CM26</t>
+          <t>2111-9985-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5260,13 +5260,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4489.96</v>
+        <v>16518.53</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1057539-4797-CM26</t>
+          <t>3328-1542-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5291,27 +5291,27 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5321,13 +5321,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>61448.92</v>
+        <v>4489.96</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5326-859-CM26</t>
+          <t>1057539-4797-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5342,37 +5342,37 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5382,13 +5382,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>14894.44</v>
+        <v>61448.92</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>617807-3629-CM26</t>
+          <t>812030-613-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5413,47 +5413,43 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2397.13</v>
+        <v>73062.75999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>608-7505-CM26</t>
+          <t>1952-1616-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5478,43 +5474,47 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>4240.14</v>
+        <v>2348.71</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>608-7503-CM26</t>
+          <t>3328-1516-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5534,52 +5534,48 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2397.13</v>
+        <v>3732.44</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>608-7589-CM26</t>
+          <t>608-7409-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5599,7 +5595,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5619,12 +5615,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5634,13 +5630,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5446.11</v>
+        <v>7749.94</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3328-1516-CM26</t>
+          <t>608-7503-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5660,48 +5656,52 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3732.44</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1952-1616-CM26</t>
+          <t>608-7505-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5726,47 +5726,43 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2348.71</v>
+        <v>4240.14</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>812030-613-CM26</t>
+          <t>617807-3629-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5791,43 +5787,47 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>73062.75999999999</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>608-7409-CM26</t>
+          <t>5326-859-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5847,32 +5847,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5882,13 +5882,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>7749.94</v>
+        <v>14894.44</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1057539-4865-CM26</t>
+          <t>608-7589-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5903,37 +5903,37 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5943,13 +5943,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>18962.89</v>
+        <v>5446.11</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1057539-4868-CM26</t>
+          <t>1057539-4912-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5989,26 +5989,22 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>21607.58</v>
+        <v>21889.66</v>
       </c>
     </row>
     <row r="90">
@@ -6075,7 +6071,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1057539-4912-CM26</t>
+          <t>1057539-4865-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6115,12 +6111,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6130,13 +6126,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>21889.66</v>
+        <v>18962.89</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1057489-8114-CM26</t>
+          <t>1057539-4868-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6151,53 +6147,57 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5146.48</v>
+        <v>21607.58</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5326-865-CM26</t>
+          <t>2111-10164-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6217,52 +6217,48 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>29971.27</v>
+        <v>4288.39</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5326-864-CM26</t>
+          <t>1952-1685-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6287,27 +6283,27 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6321,13 +6317,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>46479.34</v>
+        <v>75083.63</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1952-1685-CM26</t>
+          <t>3191-3081-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6352,47 +6348,43 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>75083.63</v>
+        <v>18897.91</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>812030-712-CM26</t>
+          <t>2111-10065-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6412,17 +6404,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6432,12 +6424,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6447,13 +6439,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>45337.65</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3191-3081-CM26</t>
+          <t>812030-712-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6473,32 +6465,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6508,13 +6500,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>18897.91</v>
+        <v>45337.65</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2111-10164-CM26</t>
+          <t>1057539-4947-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6539,43 +6531,47 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>4288.39</v>
+        <v>54188.26</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1057539-4947-CM26</t>
+          <t>5326-864-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6595,32 +6591,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6634,67 +6630,193 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>54188.26</v>
+        <v>46479.34</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>5326-865-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>61.602.140-0</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>29971.27</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1057489-8114-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>61.608.406-2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>5146.48</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>2111-10165-CM26</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>61.608.602-2</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
         <is>
           <t>BIOMET CHILE S A</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>96.863.710-k</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="n">
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
         <v>4457.05</v>
       </c>
     </row>
